--- a/agile_doc/hospital_ivr_defect_tracker.xlsx
+++ b/agile_doc/hospital_ivr_defect_tracker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="60">
   <si>
     <t>SI No</t>
   </si>
@@ -142,15 +142,69 @@
   </si>
   <si>
     <t>AI Developer</t>
+  </si>
+  <si>
+    <t>Patient ID not processed correctly in mixed input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duplicate voice input displayed in UI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deployment failure due to incorrect start command </t>
+  </si>
+  <si>
+    <t>API URL mismatch between frontend and deployed backend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final system validation issues in report navigation </t>
+  </si>
+  <si>
+    <t>Sprint 4</t>
+  </si>
+  <si>
+    <t>QA Engineer</t>
+  </si>
+  <si>
+    <t>Integration Defect</t>
+  </si>
+  <si>
+    <t>Deployment Defect</t>
+  </si>
+  <si>
+    <t>Synced conversation state with menu state (conv_state + current_menu)</t>
+  </si>
+  <si>
+    <t>Fixed duplicate rendering in speech input handler</t>
+  </si>
+  <si>
+    <t>Updated start command to uvicorn main:app --host 0.0.0.0 --port $PORT</t>
+  </si>
+  <si>
+    <t>Updated frontend API base URL to deployed endpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed report menu navigation and return flow </t>
+  </si>
+  <si>
+    <t>End-to-end IVR flow validated successfully</t>
+  </si>
+  <si>
+    <t>Frontend successfully connected to live backend</t>
+  </si>
+  <si>
+    <t>Application deployed successfully</t>
+  </si>
+  <si>
+    <t>Voice input shown only once</t>
+  </si>
+  <si>
+    <t>Patient ID now works in voice + keypad flow</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -208,12 +262,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -516,49 +577,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="35.42578125" style="2" customWidth="1"/>
     <col min="3" max="3" width="58.5703125" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="27" customWidth="1"/>
     <col min="6" max="6" width="25.85546875" customWidth="1"/>
     <col min="7" max="7" width="67" customWidth="1"/>
-    <col min="8" max="8" width="25.28515625" customWidth="1"/>
+    <col min="8" max="8" width="25.28515625" style="2" customWidth="1"/>
     <col min="9" max="9" width="21.28515625" customWidth="1"/>
     <col min="10" max="10" width="39.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -566,7 +627,7 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="5">
         <v>46058</v>
       </c>
       <c r="C2" t="s">
@@ -584,7 +645,7 @@
       <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="2">
         <v>45694</v>
       </c>
       <c r="I2" t="s">
@@ -598,7 +659,7 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>46063</v>
       </c>
       <c r="C3" t="s">
@@ -616,7 +677,7 @@
       <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="2">
         <v>46065</v>
       </c>
       <c r="I3" t="s">
@@ -630,7 +691,7 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>46068</v>
       </c>
       <c r="C4" t="s">
@@ -648,7 +709,7 @@
       <c r="G4" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="2">
         <v>46071</v>
       </c>
       <c r="I4" t="s">
@@ -662,7 +723,7 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>46073</v>
       </c>
       <c r="C5" t="s">
@@ -680,7 +741,7 @@
       <c r="G5" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="2">
         <v>46075</v>
       </c>
       <c r="I5" t="s">
@@ -694,7 +755,7 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2">
         <v>46077</v>
       </c>
       <c r="C6" t="s">
@@ -712,7 +773,7 @@
       <c r="G6" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="2">
         <v>46079</v>
       </c>
       <c r="I6" t="s">
@@ -726,7 +787,7 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="2">
         <v>46086</v>
       </c>
       <c r="C7" t="s">
@@ -744,7 +805,7 @@
       <c r="G7" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="2">
         <v>46089</v>
       </c>
       <c r="I7" t="s">
@@ -752,6 +813,166 @@
       </c>
       <c r="J7" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46091</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="3">
+        <v>46091</v>
+      </c>
+      <c r="I8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="2">
+        <v>46093</v>
+      </c>
+      <c r="I9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="2">
+        <v>46095</v>
+      </c>
+      <c r="I10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46101</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" s="2">
+        <v>46099</v>
+      </c>
+      <c r="I11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>46103</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="2">
+        <v>46101</v>
+      </c>
+      <c r="I12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
